--- a/functions in excel.xlsx
+++ b/functions in excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\excel series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C0BC25F-328E-49B9-8AA8-D59B6A00CA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C09126-131A-4206-9FAD-E58543EFA908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{47981922-77C5-4EC3-A76E-98D6CE997DC2}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="109">
   <si>
     <t>FirstName</t>
   </si>
@@ -390,6 +390,9 @@
   </si>
   <si>
     <t>mode</t>
+  </si>
+  <si>
+    <t>vlookup</t>
   </si>
 </sst>
 </file>
@@ -756,7 +759,7 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr defaultColWidth="13.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -933,7 +936,7 @@
       </c>
       <c r="Z2">
         <f ca="1">RAND()*10</f>
-        <v>5.5747359640186689</v>
+        <v>0.35686557399147945</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
@@ -1523,6 +1526,29 @@
       <c r="G17">
         <f>_xlfn.MODE.SNGL(C2:I10)</f>
         <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G19" t="e">
+        <f>VLOOKUP(B:B,A2:I10,2,1)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G20">
+        <f>VLOOKUP(A6,A2:G10,1,FALSE)</f>
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G21" t="str">
+        <f>VLOOKUP(B6,B2:G10,2,TRUE)</f>
+        <v>Flenderson</v>
       </c>
     </row>
   </sheetData>
